--- a/ML_models/component02/data/tripadvisor.xlsx
+++ b/ML_models/component02/data/tripadvisor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E3E9A0-1C97-47FE-8021-5713843A8181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEE6272-B5F2-44F4-9726-57F9FBB1CAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{108A4D46-B515-4E43-877A-4D7BDACB5F5D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
   <si>
     <t>record_id</t>
   </si>
@@ -145,6 +145,230 @@
   <si>
     <t>If you seek more adrenaline try it with rain!: There are two main routes to the peak. One is from Ihala Kotte railway station and the other from Pilimathalawa -&gt; Poththapitiya.I took the second route. Got public transport from Colombo -&gt; Pilimathalawa -&gt; Poththapitiya. Rest on foot.
 Strongly advice not to hike during rainy season because the trekking path is damn slippery when it rains. Be sure to carry some meds to prevent from leach bites. Carry a climbing rope with knots on it and it'll help your team to reach the top of so called "yam rock</t>
+  </si>
+  <si>
+    <t>A Challenging Adventure Through Sri Lanka's Cloud Forest
+The Kirigalpoththa Trail is a rousing journey through Sri Lanka's stunning cloud forest. Starting at the same point as the popular World's End trail in Horton Plains National Park, the Kirigalpoththa Trail diverges to the right, offering an adventure for those seeking a more challenging and less-traveled path. Distance: 14 km round trip Elevation Gain: 250 meters Terrain: The trail passes through plains, bog, cloud forest, and rock, providing a diverse and captivating landscape. The path is not as well marked or visible as some of the other trails in the area. Be prepared with food, water, and first aid. However, there are plenty of very clean water sources along the way where you can refill your bottles. Please note that single-use plastics are not permitted on the trail. Ensure you arrive at the starting point no later than 10:30 AM; otherwise, you may not be permitted to enter the trail. The trail offers sightings of Sambar deer, with the possibility of spotting Wildcats, Leopards, Boars, and a variety of birds. Due to the cloud forest, a clear view from the top is rare, but the joy of this hike is the adventure of getting there. The trail passes across wetlands, grassland, and forest, providing a rich tapestry of biodiversity.</t>
+  </si>
+  <si>
+    <t>Kirigalpoththa</t>
+  </si>
+  <si>
+    <t>2024.04.23</t>
+  </si>
+  <si>
+    <t>It was a once in a lifetime experience with nature. Lovely weather, amazing views with a sprinkling of adventure. Things to note: It starts at the same place as the horton plains trail. You just need to take the path towards the right instead of the horton plains one towards the left. The path is not as well marked or visible as the horton plains one. Hence, download the trail on Google maps before you start. Unless you are an experienced hiker who is used to navigating on your own it is better to travel with a guide or an experienced hiker. (We traveled with a friend who is a well known mountain climber). In certain places you do come across large areas of muddy ground (It had rained the day before our hike) and we had to deviate from the trail in several places. (For context, the sole of one my sneakers came off when I was trying to take my foot off from on one such mud pool). Take food, water and first aid. But there are plenty of very clean water sources which we used to refill our bottles. You will not be allowed to take single - use plastics. But I noticed the authorities were more lenient on the Kirigapotta hikers (than horton plains ones) on enforcing this rule. What to wear: The weather is mild and there are no leeches or other insects. But covered clothing is recommended if you want to avoid getting scratches from tree branches. Time taken: We started at 9.30 am and returned at 5 pm which included lots of snack/ photo breaks and spending one hour at the top. Start at early as possible so you can return before dark. If I remember correctly the forest office will not let you start after 11 am. Difficulty level: It's 14 kms round trip. There is no clear path. But it's mostly flat land. You will have to climb only in the last 1 -2 kms and there is steep ledge right towards the summit. In certain places you have to cut across thick forest cover and cross a few small streams. We are not regular hikers nor are we regular gym - goers. It was mildly tiring but doable. (All the aches and pains came only on the day after;) For comparison I would say, I found climbing 5000 plus Adam's Peak much more strenuous.</t>
+  </si>
+  <si>
+    <t>2023.02.06</t>
+  </si>
+  <si>
+    <t>2022.02.03</t>
+  </si>
+  <si>
+    <t>Fantastic view from the top
+We really enjoyed this hike. We were told it would take three and half hours to get to the top, but we made it in two hours and fifteen minutes. We did not take a break except for a very quick pause for a drink of water. We were lucky it was clear on the top to be able to absorb in all the scenic beauty surrounding us and enjoy our well-deserved snacks. It had rained on the previous night(s) and the path was pretty muddy. We were happy we had a local guide (required by law as well) to find the path in knee-deep reeds for the first half an hour. Then we passed through wet pasture trying not to fall into mud puddles. Then there was light climbing at first through wet muggy woods and finally some rocky ground. Then it was all uphill. It was a good climb, but I would not say it is impossible to do for anyone with some level of fitness. If you are not the regular-exercise-type of person, plan to take a lot of breaks before hitting the summit. It is worth all the trouble to get there. Make sure to take plenty of water, a change of shirt. You will be soaking-wet with your own sweat and would not be comfortable when a cold breeze blows by. Yes, a windbreaker or any long-sleeved shirt is also recommended. There are no leeches, so you only have to watch out for not-so-firm ground and slippery rocks and/or wet slopes. If you like mountains, this is a good one to climb in Sri-lanka.</t>
+  </si>
+  <si>
+    <t>2018.10.15</t>
+  </si>
+  <si>
+    <t>Kirgalpottha hike: One of the most beautiful mountain range near Hortan plains. It is like entrance to another world. It is a long hike and we need a whole day to climb it. There is plain at tge start and we have to go through wet path with mist. Its better to avoid rainy days if you want to see a clear mountain view .</t>
+  </si>
+  <si>
+    <t>2018.08.13</t>
+  </si>
+  <si>
+    <t>Best n Long hike: You have to come to hortain plains entrance 1st. Download offline google map before you go there.There is kirigalpoththa trial on the map. And use GPS always to follow the trail on the map. It will definitely make your hike very easy. It's a 14km round walk and hike. You need some strength to accomplish this hike. Though it is a very nice and scenic hike a lot of people turn back in the middle of their trail. If you are lucky enough you can see the view. Unfortunately most of the days the view is not visible due to the mist. It will take around 6hours to complete this hike. You need to start the hike before 11 am. Otherwise they will not allow you to go there.</t>
+  </si>
+  <si>
+    <t>2018.05.04</t>
+  </si>
+  <si>
+    <t>One of the best hikes in Sri Lanka !!: Kirigalpoththa mountain is the second highest mountain in Sri Lanka, located inside the Horton Plains National Park. The hike is not and not the most difficult (for experienced hikers/trekkers). You MUST have someone who knows the trek very well to show your the way, to accompany you. The path is not visible in most of the areas since it is very less frequented. Hike (up and down) is totally about a good 16+ kms. Path is through the jungle areas, muddy marshy areas and also with hilly and rocky peaks. Very good bird life as well as wildlife. Should start a bit early and should come back before it gets dark (a professional, experienced trekker would help you to reach in time). First aid, snacks and water is a must to carry with you.</t>
+  </si>
+  <si>
+    <t>This is one of the best hikes in Sri Lanka. Crossing savannahs, bamboo forests and dense eucalyptus forests you would climb the peak with never ending adventures...Come into contact with Leopard footprints and even a Leopard if you are lucky. This is a must do if you are a hiker and if you are not a hiker, then this hike will make you fall in love with hiking!!!</t>
+  </si>
+  <si>
+    <t>Kirgalpoththa</t>
+  </si>
+  <si>
+    <t>2014.08.20</t>
+  </si>
+  <si>
+    <t>2014.07.28</t>
+  </si>
+  <si>
+    <t>Kirigalpotththa</t>
+  </si>
+  <si>
+    <t>This hike is not for those who just want to have a casual visit. The trail is approximately 6-7Kms with a few steep climbs so the return journey would be 12-14kms.
+For those who do make the attempt, the hike will be very rewarding. The trail takes you through the plains, valleys, streams, forest patches and hills until at the very end it starts ascending the Kirigalpoththa mountain. The final stretch brings you out to a place close to the top of the mountain with almost a 360 degree view. The final bit along a narrow path with extreme drops on both sides will have to be negotiated on all fours if you have a fear fo hights. Do not attempt this in wet weather!</t>
+  </si>
+  <si>
+    <t>Kirigalpoththa mountain is situated closer to Hortain Plains in Nuwaraeliya district. To go on a hike you have to start it from the car park of Hortain Place National park and walk 12 km through the forest since there are roads. Be careful with leopards.</t>
+  </si>
+  <si>
+    <t>2014.07.22</t>
+  </si>
+  <si>
+    <t>We started the hike at Horton Plains National Park at 07.00 A.M. 6 Members in our group. We were dressed in hiking outfits and were carrying back packs which was almost 15 to 20 Kg. The parks elevation is around 6900 ft and our destination was 7,838 ft above sea level. The hike was approximately around 1,000 ft. The distance is 7 to 8 Km one-way!. Many ascends and descends on the way to the summit. Within the first Km of our journey we unexpectedly came across the Sri Lankan Sambar Deer just 20 ft away from us. The Small Herd consisted about 4 female deer. Once they had spotted us one of the deer made a warning sound and fled towards the covers without permitting us an opportunity to capture their beauty in a photograph. Further towards the mountain around two km from the starting point there is a small stream. This is the junction which separates the path into two. One leads to the Kirigalpoththa Summit and the other leads to Bogowanthalawa about 4967 ft above sea level. From that point on wards the hike is very challenging and has the most breath taking views. At some points we were amazed by the view we even forgot to take photographs. :(. After passing few plains we were almost lost due to a trail which was misleading us. Getting back to the track took us around one hour. Exhausted we continued our ascend through the correct path. We reached the summit at around 1.00 PM and Stayed there for 1 1/2 hours. With the greatest regret we started our descend promising to our self that we will return to relive the adventure once again. We reached the Horton Plains Nature park at around 5.15 PM. This trail is the best trail that i have being so far. All hikers should make sure not to carry heavy back packs so that you could enjoy your hike. Be a careful observer so that you could get a glimpse of the enchanted wildlife in this terrain.</t>
+  </si>
+  <si>
+    <t>2023.08.23</t>
+  </si>
+  <si>
+    <t>2015.11.21</t>
+  </si>
+  <si>
+    <t>Having been to Horton Plains quite a few times we decided to do the Kirigalpoththa hike this time. The hike starts from the same location ( visitor center) where the worlds end loop starts. We were lucky that it didnt rain during the day we hiked bu it has been raining all through out the previous week.
+The trail was slippery and muddy, there were places where got in the mud above ankle and our shoes were all soaked in muddy water. We left Nuwaraeliya a little late by purpose. Had breakfast at the hotel and carried packed lunch.
+The sign at the beginning of the trail says 7km to the top of kirigalpoththa, the second highest peak of Sri Lanka. But we measured and it was actually 5.6 km to the top.
+It was full of mist when we got to the top so werent treated with the otherwise what would have been stunning views. Would not suggest this for families with kids or elderly people who arent used to regular physical activity. BUt all in all a day well spent surrounded by nature and good company</t>
+  </si>
+  <si>
+    <t>2015.07.24</t>
+  </si>
+  <si>
+    <t>We set out to Horton's Plains at 5am. Visibility is quite low and We couldn't see more than 10m ahead. We started the trek at about 6am. Did not hire a guide. Just followed the trail. At the time we didn't quite understand why we were walking through the fog and mist.It beings with a steep climb. The trail circles through the park. At the fork in the road, our guide back at the Grand Hotel, Nuwara Eliya suggested we turn to the left. This brings you through the forest. Its a gradual uphill climb. Trees on either side so not much to see around. At about 8 am we got to the Mini World's end. By this time the Sun was up and the skies clear. Breathtaking view of the surrounding mountains and lakes. We stopped here for about 15 minutes for pictures.The next stop was the world's end. There's a climb higher up which is off the trail. Great place for pictures at the cliff. The view makes walking through the cold mist worth it!The rest of the trek from World's end was through the plains. Picturesque gradual slopes and grass covered plains. The mist is unpredictable and disappears as suddenly as it appears.There is a deviation off the trail to see Baker's Falls. Its a steep climb with a mixture of concrete stairs and tree roots as stepping stones. Stopped at the falls for about 20 minutes.There is an alternative route from here which is along the river. We didn't go back to the point we deviated off the trail to see the falls.Walking through the plains we figured we would have missed these magnificent views had we walked straight at the fork as the fog/mist would have swallowed the landscape. Back at the starting point at 10:30 am.The terrain changes from flat and sandy to steep and rocky quite randomly. Would suggest wearing comfortable and strong shoes. It does get quite cold in the morning. But was warm when we were done.The park does not allow any plastic (excluding water bottles) inside. So pack all food in paper bags or carry fruit.The fog was back when we left the park at 11am. It's essential to get the timings and the route correct to ensure you get to the view points for a view and not just fog! A definite must do if you are in Nuwara Eliya</t>
+  </si>
+  <si>
+    <t>2015.04.13</t>
+  </si>
+  <si>
+    <t>The hike up Kirigalpoththa which is the 2nd tallest mountain in Sri Lanka is not a popular one due to the distance and time it takes.The Park opens at 6am. Try to start the hike as early as possible to avoid the mid day sun/ rain/ mist. Be prepared with shades, cap, hiking staff and rain coat and wear shoes which would get covered in mud if it rains!The walk starts at the Farr's Inn and is 7 Kms one way. It takes approx 3 hrs one way. It is advisable to take a guide with you and the Park will provide one. We (party of 5) gave Rs.2000 to the guide as a "thank you".The walk is through tall grass, small streams, places where water collects and can get swampy and thick jungle. The guide will explain the fauna and flora around.Avoid getting late to return, specially if it rains as the streams swell and become rivers.Fantastic view from the top! Be careful when walking up the last bit over the rocks, with the precipice on one side. Take the path through the jungle.The Park is very strict on restricting polythene and plastic items, cigarettes, lighters. There are lockers to keep these items if you must take them up to the Park.A shorter and easier walk is up Thotupola Mountain which is also within the Park</t>
+  </si>
+  <si>
+    <t>2018.01.25</t>
+  </si>
+  <si>
+    <t>This is the 2nd most highest peak in Sri Lanka. Situated in Horton plains national park. Can enter the park via main gate at pattipola side or ohiya side. Have to buy tickets. Best to start the hike early in the morning. 7Km track. Better to bring the rain coats. Lot of mist and sometimes the wind. Small foot path all the way up. Lots of birds and Sambar. If you are really lucky can spot leopards too. Last part of the hike is difficult. Because have to walk along the ridge of the mountain to reach the top. If you slipped, there is nothing to hold onto. Better to avoid that part if there is rain or strong winds. View is fantastic and best part is not many tourists are along the track so you can enjoy the nature. Importantly no polytene products are allowed in the park.</t>
+  </si>
+  <si>
+    <t>2018.05.28</t>
+  </si>
+  <si>
+    <t>The trail starts from the Horton Plains Visitor Center. The first part leads through plains and some little woods from time to time. In the second part, when the ascent to the summit starts, these hills are all covered by wood. This is where we had an encounter with a big male Leopard. He came pretty close (about 8m) when we were taking a rest in the woody hills towards the summit. On the one hand, this was a nice encounter. On the other hand, (theoretically) an accident could have resulted out of this situation. The leopard left after some seconds (I was standing, shouted something &amp; grabbed my hiking-sticks as a reaction). This is not about alarming or intimidating people! I thought, I should share this experience and inform that this kind of an encounter may be rare (I guess), but possible!</t>
+  </si>
+  <si>
+    <t>This is one of exiting and breathtaking hikes that you would ever get in your lifetimes.
+This is a very popular hike among foreigners due to the visibility of the largest Sri Lankan tiger, Leopard.It is recommended to hike with an experienced guide</t>
+  </si>
+  <si>
+    <t>2016.12.26</t>
+  </si>
+  <si>
+    <t>Thotupala Kanda</t>
+  </si>
+  <si>
+    <t>Folklore of India and Sri Lanka talk about an all powerful mythical king called Ravana who travelled around in a flying machine called the "Dandumonara". In folklore, Thotupola, as the literal name suggests is said to be the place where this this machine was parked.
+Thotupola is the third highest mountain in Sri Lanka and the hike to it's summit is the easiest out of the trails in the Horton Plains Forest Reserve.
+You will come to the trail entrance a couple of hundred meters after you pass the Pattipola entrance and move towards the famous Horton plains trail entrance. There is a sign board indicating the place.
+It's a 2 km (one way) relatively easy hike with very little elevation gain. The round trip including photo stops took us 2 hours. But then again, my legs were feeling like jelly after a more strenuous hike the day before, so we pretty much moved at the pace of sloths.
+There is a clear path right to the top. But in certain places the path can get very narrow, sandwiched between thick shrub jungle on both sides. So it's advisable to be fully covered to avoid being scratched from tree branches. A hiking stick would also be useful to pave the way when the shrubs become too thick. The vegetation is quite different from the Horton plains trail. Here you mostly walk through a scrub jungle (a plus on a sunny day though) and there are only couple of open areas where you would get a nice view of the surrounding areas. The day we visited, there was a heavy mist, so even the open areas didn't offer much of a view.
+The supposed summit (assuming what we thought as the summit was the actual summit) is a bit of an anti climax being marked by a telecommunications tower and covered in shrub jungle, hence offering no views. Its better to remember that the highlight of this trail is the journey and not the end destination....
+On the subject of lepords...... Post corona, Horton Plains had had increased sightings of leopards. At the Pattipola entrance ticket counter, we were told not to get down from the vehicle until we got to the Horton plains trail car park which is 5kms away, due to the presence of leopards. However when we told them that we would be taking the Thotupola trail which would basically require us to get down from the vehicle on the path between the ticket counter and the main car park they said that was perfectly fine....! At the entrance to the Thotupola trail there was another sign warning about the presence of leopards. We were a little apprehensive at first since there were only 2 of us. But another group of 4 boys joined us at the trail. Plus it was a long weekend and the route to the main Horton plains trail was quite busy with vehicular traffic. So, our advice would be to either go with a large group or in a really busy period.There is not much parking space at the entrance to this trail, but you can generally manage to park there since not many people take this trail. [While the ticket office will tell you to park only at the main car park, those who take this trail will be allowed to park at its entrance.] Surprisingly, there were also two newly built, very clean washrooms at the entrance to the trail. The park opens at 6 am but there are separate closing times for each trail. Do check those before visiting. I love any and every kind of hike and loved this hike as much as any other one I have taken. Also loved the misty weather even if it meant no stunning views. But objectively, this hike is neither as adventurous as the Kirigalpotta hike nor as picturesque as the horton plains trail (all in the same Forest Reserve), hence the four star rating</t>
+  </si>
+  <si>
+    <t>2024.08.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thotupola kanda is a third highest peak in Sri Lanka. It’s a 2km hike with a beautiful scenery on top .
+On the peak it’s a fantastic scenery with mist clouding around you on and off .
+On the way if you are lucky you can spot leopards of the cloud forest .
+Path is not difficult and it will take about 2hrs to climb up and down </t>
+  </si>
+  <si>
+    <t>2024.06.28</t>
+  </si>
+  <si>
+    <t>Kingdom of Lepords: It is not a hard hike to top of the mountain. But there are so much trees and bushes every where. Forest is so thik and don't go out of the road. Never hike alone or walk at night. This is one of the greatest lepord kingdom at Horton Plains.</t>
+  </si>
+  <si>
+    <t>2024.06.24</t>
+  </si>
+  <si>
+    <t>So if you are going here, please make sure to get there as early as 6-7 am. We made the mistake of getting there later (mid day) and it was all misty. Though the forest trail was very enjoyable when we were heading to the top it was very windy and covered in mist ( we enjoyed it nevertheless) I would not encourage toddlers / children under the age of 10 as the way to the top will have grass reaching your waist or taller. do not wear shorts, you may bruise yourself. wear long thicker trousers.
+Due to the time we got to the top we could view anything. but the treck itself was very enjoyable. if you take a small snack with you, there are small patches where you can lie down and enjoy. in the event you do decide to take children under the age of 10, its best for an adult to scope when you arrive at the narrow route with tall glades and then decide if the children could make it through. If the kids are well seasoned travel enthusiasts, they will enjoy the trail further uphill. You can always turn back if the going gets tough</t>
+  </si>
+  <si>
+    <t>2018.08.28</t>
+  </si>
+  <si>
+    <t>Quite close to the entrance gate and is one of the more easier hikes to the 3rd highest mountain in Sri Lanka. Walking through the bushes in the mist is an absolutely amazing expireince. But its too bad that there is no realy view at the top mostly due to the heavy mist.</t>
+  </si>
+  <si>
+    <t>2016.08.25</t>
+  </si>
+  <si>
+    <t>its not hard at all. it has a perfect trail and very beautiful view of hortan plains entrance and other area. Leapod activities are much higher . but its so hard to spot one.</t>
+  </si>
+  <si>
+    <t>2016.02.28</t>
+  </si>
+  <si>
+    <t>Amazing and serene. This trail is very peaceful and beautiful. You will see some rare birds like the Dull Blue Flycatcher, Sri Lanka Whistling Thrush etc. Also you will see the rare horned lizard found in Horton Plains. If you are lucky you might get a brief glimpse of a leopard</t>
+  </si>
+  <si>
+    <t>2016.02.03</t>
+  </si>
+  <si>
+    <t>not a difficult hike , slippery and wet conditions are there but that is part of what makes it what it is. there is no great view when you are at the summit point so don't be dissapointed , the fun is in the hike itself. there are places which provide panoramic views throughout the hike.</t>
+  </si>
+  <si>
+    <t>2015.10.22</t>
+  </si>
+  <si>
+    <t>Little Adam's peak</t>
+  </si>
+  <si>
+    <t>It is an easy walk up, only the last 200 meters are stairs and it is a bit steeper, if you go up 30 minutes after it gets light you can take a beautiful sunrise picture, where the sun comes out just behind the mountain top.</t>
+  </si>
+  <si>
+    <t>2026.03.10</t>
+  </si>
+  <si>
+    <t>With our guide we set off at 6 am. Unfortunately it was raining on and off but still hot and humid. The walk to the rock was pretty and the pathways that started upwards between the boulders. We were pretty tired by the time we had climbed to the lions paws by and were disappointed that mist obscured much of the view. I’m afraid of heights, but as I’d climbed that far, pushed on to the top, clinging tightly to the railings and not looking past the steps in front of me. At the top I had a short look around, but there were no views visible because of the mist. On the way down I could not bring myself to climb the spiral staircase on the cliff edge to view the paintings.
+Overall an interesting place but without the view, I could have skipped the climb!</t>
+  </si>
+  <si>
+    <t>Sigiriya</t>
+  </si>
+  <si>
+    <t>2025.03.10</t>
+  </si>
+  <si>
+    <t>2018.12.27</t>
+  </si>
+  <si>
+    <t>It was not a very easy hike, a difficult path and through steep rocks quite adventures. Recommended to do the trial early morning or evening, we reached the top around 1-3pm and was very sunny so we couldn't enjoy the view from the top. very nice and beautiful view at the top worth the difficult walk. Beware of leeches!</t>
+  </si>
+  <si>
+    <t>Hanthana</t>
+  </si>
+  <si>
+    <t>2016.04.15</t>
+  </si>
+  <si>
+    <t>This is the Best Mountain for the First Time Hikers. There are several roots to climb this and each one is different from other. If you are a Adventure lover you can use the root near Amaya Hills Hotel (go to "gatambe water bord Holt" by bus then took a "three wheel" to go to the amaya hills) , it goes through a Pines forest and you have to climb up through a small "ela" so its really adventures and joyful. There is a amazing view of kandy in the Top. There are so many leaches so carry salt. Bring lot of Water. It takes like 3 4 hours to climb in a normal speed so start your hiking journey in early morning (like 8.00am). Take a guide with you, if not you will get lost sometimes (because some roots are hard to find).</t>
+  </si>
+  <si>
+    <t>2014.10.02</t>
+  </si>
+  <si>
+    <t>We hiked up Hanthana Mountain Range through Peradeniya/Mahakanda route with our usual 5 member crew last week and I would say it was super awesome and loved every minute of it.It was a very cloudy day and we started at 8 am from Peradeniya, trailed over 6 KM through Mahakanda, since the road was closed due to construction to reach the actual starting point. We went to the middle part (not the telecom tower side) of Hanthana mountain range. Because of the last night overcast the path was very floody, slippery. It started raining like cats and dogs when we were at the middle part. But however with the heavy shower it took nearly five hour to reach the final point. It was so cool and windy at the peak. Overall this was an excellent experience for us. Yeah, It was awesome, marvelous, challenging, adventures and absolutely stunning! No wonder, it’s the Paradise of the Hill Capital. We thoroughly enjoyed our hike up Hanthana Mountain.If you have the time and are willing, take the hike up the Hanthana Mountain as you will not be disappointed! Enjoy as we did!Tips:Take a guide, Always carry loads of water. Don’t forget to take Hat/Raincoat,  Start your journey in the early morning,  Avoid taking too much items. (e.g. extra pair cloths/water bottles/food/energy drink), Carry salt for lechers, Of cause don’t forget to take your camera.</t>
+  </si>
+  <si>
+    <t>Pettigala</t>
+  </si>
+  <si>
+    <t>2024.08.08</t>
+  </si>
+  <si>
+    <t>Went in june 2024. Stayed at Victoria Golf club. The hotel arranged transport for us to go to Pettigala, since we went there from colombo in the train to Kandy and then hired a van for the rest of the journey to the location.
+The weather was lovely as it was just after a showery spell. Pettigala climb is a moderate intensity hike for moderately fit persons. We were all in our late 50s. The climb starts from the Bambaragala temple. No clear markings to indicate the route. So we followed the well trodden pathway through a forest of mainly vines. We were helped by a guide dog. Felt sad we had no food to give in return for the favour. Lots of monkeys on the way. Some points during the hike can be a bit difficult. There are no rest areas on the way. Take enough water to drink. It took us about an hour to reach the top. The awesome almost 360⁰ view from the top was well worth the effort.
+While returning we got a bit lost close to the end of the trail. Fortunately we encountered a group who had done the hike mutiple times.</t>
   </si>
 </sst>
 </file>
@@ -519,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCCE22E-7342-4B13-9D46-BE297CEF71C1}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.88671875" customWidth="1"/>
@@ -724,6 +948,426 @@
         <v>31</v>
       </c>
     </row>
+    <row r="15" spans="1:5" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
